--- a/Result/profitability/9917.xlsx
+++ b/Result/profitability/9917.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.57875</v>
+        <v>1.5925</v>
       </c>
       <c r="N2" t="n">
-        <v>34.1475</v>
+        <v>34.19875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.93</v>
       </c>
       <c r="M3" t="n">
-        <v>1.49</v>
+        <v>1.50875</v>
       </c>
       <c r="N3" t="n">
-        <v>35.33875</v>
+        <v>35.40125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>1.36125</v>
+        <v>1.38125</v>
       </c>
       <c r="N4" t="n">
-        <v>36.81625</v>
+        <v>36.72875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.22625</v>
+        <v>1.23625</v>
       </c>
       <c r="N5" t="n">
-        <v>38.69374999999999</v>
+        <v>38.67375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.88</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1275</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>40.11375</v>
+        <v>40.1375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02125</v>
+        <v>1.01625</v>
       </c>
       <c r="N7" t="n">
-        <v>41.595</v>
+        <v>41.8725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9037500000000001</v>
+        <v>0.9225000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>43.145</v>
+        <v>43.0275</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.7899999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>43.65625</v>
+        <v>43.65624999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4858</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3257</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1601</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="G75" t="n">
+        <v>842</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>108</v>
+      </c>
+      <c r="J75" t="n">
+        <v>950</v>
+      </c>
+      <c r="K75" t="n">
+        <v>775</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.67125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9399999999999977</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02772861356932144</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.04790419161676662</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1599999999999966</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.004830917874396046</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
